--- a/app/src/main/assets/Survey_Questionnaire_26050601.xlsx
+++ b/app/src/main/assets/Survey_Questionnaire_26050601.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Salman\AndroidStudioProjects\CREF_WSS_01\app\src\main\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FBA5B07-7351-4DBE-A37E-7F787E1A5EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94AF62E1-B635-4DAD-BA80-2D8B7882F912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{5C01FDD9-1395-4563-A01A-D87C8ECFACAC}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4804" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4807" uniqueCount="669">
   <si>
     <t>id</t>
   </si>
@@ -2035,6 +2035,15 @@
   </si>
   <si>
     <t>GEOMETRY</t>
+  </si>
+  <si>
+    <t>Tag</t>
+  </si>
+  <si>
+    <t>SCHEME_NAME</t>
+  </si>
+  <si>
+    <t>INFO_PROVIDER</t>
   </si>
 </sst>
 </file>
@@ -17698,15 +17707,17 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD53D293-92AF-46B4-A9A3-9308FCA86775}">
-  <dimension ref="A1:I287"/>
+  <dimension ref="A1:J287"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="114" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="255.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -17734,8 +17745,11 @@
       <c r="I1" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -17755,7 +17769,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -17773,7 +17787,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <f t="shared" ref="A4:A68" si="0">A3+1</f>
         <v>3</v>
@@ -17791,7 +17805,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -17811,8 +17825,11 @@
       <c r="F5" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J5" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -17833,7 +17850,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -17853,8 +17870,11 @@
       <c r="F7" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J7" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -17872,7 +17892,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -17893,7 +17913,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -17914,7 +17934,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -17935,7 +17955,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -17953,7 +17973,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -17974,7 +17994,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -17992,7 +18012,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -18010,7 +18030,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -23954,6 +23974,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
